--- a/out/Attention-S4_repeat_5_000006.xlsx
+++ b/out/Attention-S4_repeat_5_000006.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>-0.0004499999204052146</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0.5791847404061293</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>1.159465998829599</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>-0.133757660132265</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.4449770803534591</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.4449770803534591</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0.4443268406489261</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>1.997676836956239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>4.443658681241157</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0.382233015717621</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>3.207532332316912</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0.6695173772783545</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>4.164521438840861</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0.3666518416718266</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>4.227731138341602</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0.1514325502666</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>4.163559948754264</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0.1886724529863682</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>4.389497328179329</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0.1136051879650082</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>4.427907218151965</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0.0863695851194413</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>4.48699445300386</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0.03820228665973414</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>4.476951467213387</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0.03031254143431289</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>4.499363028430882</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0.01503139786272664</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>4.499089645291213</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0.0087400574413624</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>4.501527917636735</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0.0043675287206812</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>4.501517473543307</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0.002153860769948658</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>4.501457789557337</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0.001249957444491429</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>4.501799831866843</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0.0004146103814267188</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>4.501378067704151</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0.0002061043678434781</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>4.501375403620467</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>0.0001099712181150998</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>4.501389120225419</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>4.951415028015501e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>4.50138047478123</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>2.991040894755449e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>4.501388383345017</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>1.046497567870175e-05</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>4.501379378763374</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>3.872723086529542e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>4.501376650932913</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>4.501372331941764</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>4.501367507768875</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>4.50136664983529</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>4.501366878156325</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>4.501366082492113</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>4.501366144761486</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>4.501366172436763</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>4.501366324650786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>4.501365978709824</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>4.501366054816835</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>4.501366220868497</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>4.501366580647097</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>4.501366601403554</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>4.501366705185844</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>4.501366933506878</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>4.501366808968132</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>4.501366836643409</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>4.501366891993963</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>4.501367154909094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>4.501367071883263</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>4.501366864318687</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>4.501366878156325</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>4.501367016532709</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>4.501366732861121</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>4.50136655989064</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>4.501366456108351</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>4.501366601403554</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>4.501366843562229</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>4.501366670591747</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>4.50136637308252</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>4.501366359244882</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>4.501365992547463</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>4.501365992547463</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>4.50136593027809</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>4.501365826495801</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>4.501365653525321</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>4.501365701957055</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>4.501365342178454</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>4.501365300665539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>4.501365356016094</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>4.501365411366647</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>4.501365452879563</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>4.501365183045612</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>4.501365238396167</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>4.50136538369137</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>4.501365349097274</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>4.501365335259636</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>4.501365425204286</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>4.50136574346997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>4.50136556358067</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>4.501365605093587</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>4.501365418285467</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>4.501365487473659</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>4.501365286827902</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>4.501365328340817</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>4.501365356016094</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000006.xlsx
+++ b/out/Attention-S4_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000006.xlsx
+++ b/out/Attention-S4_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01288634538650513</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01016920059919357</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.008844666182994843</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.008511163294315338</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.007534004747867584</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.009060405194759369</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.008337743580341339</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.009091965854167938</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.008800014853477478</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.008842036128044128</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.009750328958034515</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.00972776859998703</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01032888889312744</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01004280149936676</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01054767519235611</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01076087355613708</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01102049648761749</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01106702536344528</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01134777814149857</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01065297424793243</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01093816757202148</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01121978461742401</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01133814454078674</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01203244924545288</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01108627021312714</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01399083063006401</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01388613134622574</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01037359982728958</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01146003603935242</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01261430978775024</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01246917247772217</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01338785141706467</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01439984887838364</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01467256620526314</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01162204891443253</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01297518238425255</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01352205127477646</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0129999928176403</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01409392058849335</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01487754285335541</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01674665510654449</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01722308993339539</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01881827414035797</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-9.770429748657625e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.1257528312016157</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0115315169095993</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.2517440691349432</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.02904159478076405</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01384219154715538</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.09661353212336497</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0183689221739769</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.09661353212336497</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0184081494808197</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.09649278101067943</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.3709735329308994</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0175003819167614</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.8391785418834192</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.07098154342830479</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.02437387779355049</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.6096268569047153</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.1243309050686419</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01998920738697052</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.7873422295672873</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.06808812809128699</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01839130371809006</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.7990804564662553</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.02812158530001873</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01464418321847916</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.7871636443687968</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.03503659163188461</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01811500266194344</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.8291209440709786</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.02109714451432236</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01237551122903824</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.8362538841597845</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.0160386033212712</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.02393696829676628</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.8472267286846693</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.007091189072734838</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.00752568244934082</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.8453588771094345</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.005627098978995626</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01600267365574837</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.8495182523705126</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>0.002786651973848432</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03034890443086624</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.8494634075548858</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.001618334016061284</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01556853204965591</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.8499123573383415</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.0008066670080306419</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01357909291982651</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.8499063467581244</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.0003974507427334383</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01545443758368492</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.8498911591218228</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.0002286356944531915</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01568616926670074</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.8499507680624225</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>7.311895398901677e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01014760881662369</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.8498681789895806</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02155319973826408</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.8498636152801702</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01695625856518745</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.8498621993109056</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.02361719682812691</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.8498565024496021</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.02355360984802246</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.8498541935448002</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01656226813793182</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.8498481940112035</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02164007350802422</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.8498439514010495</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01941682398319244</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.8498441797220841</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.02330037951469421</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.8498442696667341</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.02178894728422165</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.8498434117331494</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02675530314445496</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.849843640054184</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01882276684045792</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.8498428443899723</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01794702187180519</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.8498429066593454</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01819176599383354</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.8498429343346222</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01940729469060898</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.8498430865486455</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01583294570446014</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.8498427406076838</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01538345590233803</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.8498428167146954</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01874314248561859</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.8498429827663571</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02431440725922585</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.8498433425449571</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.02632809057831764</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.8498433633014147</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.02072517946362495</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.8498434670837033</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01735752075910568</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.8498436954047379</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01958239823579788</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.8498435708659917</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01821130886673927</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.8498435985412686</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0216725654900074</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.8498436538918226</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02196389809250832</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.8498439168069533</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.02378356456756592</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.8498438337811225</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.02172132208943367</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.8498436262165457</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0203070268034935</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.849843640054184</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01955363899469376</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.8498437784305688</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01620788872241974</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.8498434947589801</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01947592198848724</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.8498433217884994</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.02026954665780067</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.8498432180062109</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.02197467908263206</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.8498433633014147</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02496873959898949</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.849843605460088</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01962172240018845</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.849843432489607</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01956422626972198</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.8498431349803801</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02176331728696823</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.8498431211427415</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.02123687788844109</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.8498427544453223</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02285783365368843</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.8498427544453223</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01916880905628204</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.8498426921759492</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0167955756187439</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.8498425883936608</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.02073711156845093</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.84984241542318</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01633067801594734</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.8498424638549146</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.01360160857439041</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.8498421040763144</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.01465592533349991</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.8498420625633991</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01393196359276772</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.8498421179139528</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01733949035406113</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.8498421732645067</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01300443336367607</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.8498422147774222</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0119660347700119</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.8498419449434721</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01190995424985886</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.849842000294026</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01178346574306488</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.8498421455892299</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01131113618612289</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.8498421109951336</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.009972020983695984</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.8498420971574951</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01078277826309204</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.8498421871021453</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01125375181436539</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.8498425053678299</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.007508471608161926</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.8498423254785298</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.008003778755664825</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.8498423669914452</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.006997555494308472</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.8498421801833259</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.006801553070545197</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.8498422493715184</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.006921827793121338</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.8498420487257605</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.006533734500408173</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.849842090238676</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.004945792257785797</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.8498421179139528</v>
       </c>
     </row>
   </sheetData>
